--- a/cache_proyectos/barnes_noble/FINAL_FOR_REVIEW_2026-10-24_rev13/Take-off/Barnes_Noble_ColoradoSprings_Takeoff_FINAL_rev13.xlsx
+++ b/cache_proyectos/barnes_noble/FINAL_FOR_REVIEW_2026-10-24_rev13/Take-off/Barnes_Noble_ColoradoSprings_Takeoff_FINAL_rev13.xlsx
@@ -2281,7 +2281,7 @@
     <t xml:space="preserve">reglas.py compuerta OK</t>
   </si>
   <si>
-    <t xml:space="preserve">{"canon": "f3623ea48012f20791133dc93e86ea7c66aaa059d25e649d281e1ec80dbfdf87", "evidencias": "82f4ec13c901d7191f9772989e98854d158340ab19499f6cfbada96ca6cbd21e", "familias_out": "b185337f275b61687384e9e03306738f9c81a7254fdb31cb674cf3d3b32b5c00", "reglas": "26cd43ad2b0dabf9c000cc5efad076b676363c3a45b7af4570136de43fd09305", "version": "v73"}</t>
+    <t xml:space="preserve">{"canon": "c7127044ce1e61197dce878326d3f645ed6b2bbe7ae262f4e911ae5ab5a71334", "evidencias": "82f4ec13c901d7191f9772989e98854d158340ab19499f6cfbada96ca6cbd21e", "familias_out": "b185337f275b61687384e9e03306738f9c81a7254fdb31cb674cf3d3b32b5c00", "reglas": "26cd43ad2b0dabf9c000cc5efad076b676363c3a45b7af4570136de43fd09305", "version": "v73"}</t>
   </si>
 </sst>
 </file>
